--- a/excel/output_stats_vfvv/floyd-warshall/EfficiencyStats.xlsx
+++ b/excel/output_stats_vfvv/floyd-warshall/EfficiencyStats.xlsx
@@ -490,28 +490,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52.2164</v>
+        <v>52.2865</v>
       </c>
       <c r="D2" t="n">
         <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>42.6597</v>
+        <v>42.7438</v>
       </c>
       <c r="F2" t="n">
-        <v>354.4</v>
+        <v>364.1</v>
       </c>
       <c r="G2" t="n">
-        <v>356.26</v>
+        <v>371.4</v>
       </c>
       <c r="H2" t="n">
-        <v>351.288</v>
+        <v>333.773</v>
       </c>
       <c r="I2" t="n">
-        <v>351.445</v>
+        <v>333.229</v>
       </c>
       <c r="J2" t="n">
-        <v>108753000</v>
+        <v>53270600000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
